--- a/artfynd/A 30642-2021 artfynd.xlsx
+++ b/artfynd/A 30642-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30642-2021 artfynd.xlsx
+++ b/artfynd/A 30642-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>2278105</v>
       </c>
       <c r="B2" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517759.9350295293</v>
+        <v>517760</v>
       </c>
       <c r="R2" t="n">
-        <v>6450876.123191474</v>
+        <v>6450876</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1978-07-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1996-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>87708274</v>
       </c>
       <c r="B3" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517741.9604769543</v>
+        <v>517742</v>
       </c>
       <c r="R3" t="n">
-        <v>6450880.78623849</v>
+        <v>6450881</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,19 +860,9 @@
           <t>2020-06-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
